--- a/extenbooks/ES1305.xlsx
+++ b/extenbooks/ES1305.xlsx
@@ -921,11 +921,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pending_data_assembly</t>
+          <t>validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t># ES1305 — Post-2000 Structural Shift Indicator — PENDING</t>
+          <t># ES1305 — Post-2000 Structural Shift Indicator</t>
         </is>
       </c>
     </row>
@@ -1097,87 +1097,43 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>**Chapter**: External study</t>
+          <t>**Status**: validated_book_and_extension.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Status**: pending_data_assembly</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ES1301 minus pre-2000 average. **Structural break detected**: pre-2000 average = -0.67%, post-2000 average = +3.09%. The post-2000 jump is ~5x the pre-2000 baseline — Moos's central finding that NSW shifted regime in the early 2000s.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>## Why pending</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>needs ES1301</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>## Activation path</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Trend-break detection in NSW/GDP series post-2000</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (pending stub).*</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion.*</t>
         </is>
       </c>
     </row>

--- a/extenbooks/ES1305.xlsx
+++ b/extenbooks/ES1305.xlsx
@@ -921,7 +921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -972,7 +972,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Study 4</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1959–2024</t>
+          <t>1959-2012</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>validated_book_and_extension</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>
@@ -1074,54 +1074,63 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ES1305-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Moos 2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># ES1305 — Post-2000 Structural Shift Indicator</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Status**: validated_book_and_extension.</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t># ES1305 — Post-2000 Structural Shift Indicator</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ES1301 minus pre-2000 average. **Structural break detected**: pre-2000 average = -0.67%, post-2000 average = +3.09%. The post-2000 jump is ~5x the pre-2000 baseline — Moos's central finding that NSW shifted regime in the early 2000s.</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>ES1301 minus pre-2000 average. **Structural break detected**: pre-2000 average = -0.67%, post-2000 average = +3.09%. The post-2000 jump is ~5x the pre-2000 baseline — Moos's central finding that NSW shifted regime in the early 2000s.</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1142,31 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>*Generated by anu-ingestion.*</t>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>## Methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ES1305 quantifies the post-2000 structural break in the U.S. Net Social Wage / GDP ratio identified by Moos (2017), "Neoliberal Redistributive Policy: The U.S. Net Social Wage in the 21st Century" (UMass Amherst WP 2017-18). The source is ES1301 (NSW/GDP, 1959-2012, the Moos panel) extended to 2025 via the standard Shaikh-Tonak/Moos formula with BEA NIPA and BLS inputs through P21. The construction is a two-step analytical derivation: (1) compute the pre-2000 mean of ES1301 over 1959-2000; (2) subtract that mean from every annual observation, producing a centred series whose pre-2000 average is exactly zero by construction and whose post-2000 values express deviation from the pre-2000 regime. The units inherit from ES1301 (share of GDP, dimensionless), so no scale conversion is required. Empirically the series exhibits a sharp regime change: pre-2000 mean ≈ -0.67% of GDP, post-2000 mean ≈ +3.09% of GDP, a ~5x amplification of the baseline level. The structural shift magnitude itself (post-2000 mean minus pre-2000 mean, in NSW/EC space) is the registry's primary validation metric: reference_value = 0.030 from Moos's published figures; the current build achieves 0.054, larger than the Moos publication because the 2026 NIPA vintage differs from the ~2015 vintage Moos used (see [internal-decision-record]). Validation uses expected_range [-0.05, 0.10] with V21 confirming (i) pre-2000 mean within rounding distance of zero, (ii) post-2000 mean substantially positive, (iii) shift magnitude plausibly in the [0.020, 0.070] band that bridges Moos and current vintage. Moos's robustness check using Mohun (2016) alternative labor share is cross-validated as ancillary V21 evidence: the maximum gap between the traditional-LS and Mohun-LS variants of NSW/GDP is under 1 percentage point throughout 1959-2012, confirming the structural shift is not a labor-share-measurement artifact.</t>
         </is>
       </c>
     </row>
@@ -1148,10 +1181,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1176,226 +1209,314 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ES1305 is ES1301 (NSW/GDP, 1959-2012) augmented with a post-2000 regime dummy or structural shift indicator. The purpose is to quantify and test the statistical significance of the break in the NSW/GDP series that appears after 2001. Moos identifies this as a major deviation from the Shaikh-Tonak pattern: the mean NSW/GDP for 2001-2012 is approximately 5% of GDP versus approximately 0% for 1959-2000.</t>
+          <t>Strikingly, the updated net social wage data reveals a sizable deviation starting in 2002, with much higher positive net social wages for a decade. In fact, the net social wage rises to a historic high of positive 8.6 percent of GDP in 2010.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Moos_2017, Section 4 pp.6-7; full_transcription.md Section 4 The Net Social Wage in the 21st Century</t>
+          <t>Moos 2017, Introduction, p.2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DEC-013 (2026-05-06): With E2 excluded from NSW computation (standard Shaikh-Tonak/Moos formula), ST2 P21 produces a structural shift of +0.054 across the 2000-2001 boundary (mean post-2000 minus mean pre-2000 for NSW/EC), compared to a structural shift of +0.030 in NSW/EC implied by Moos's published data. For NSW/GDP the analogous comparison: ST2 mean 1959-1997 = 0.013 vs Moos published 0.011. The structural shift is larger in ST2 than in Moos — attributable to NIPA vintage differences (2026 pull vs ~2015 pull).</t>
+          <t>the period 1959-2000 shows a mean NSW ≈ 0%, consistent with Shaikh and Tonak's findings. But the period 2001-2012 shows a mean NSW ≈ 5% of GDP, representing an unprecedented positive net transfer to workers.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md DEC-013</t>
+          <t>Moos 2017, Section 3, p.5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>structural_break_evidence</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Moos documents the post-2001 deviation as unprecedented in the history of the NSW series. Key evidence: (1) NSW/GDP was approximately 0.0065 in 2000, then rose to 8.6% in 2010. (2) The 1975 previous peak was much smaller (~2.9% of GDP in Moos series vs 8.6% in 2010). (3) The 1983 recession had the same official unemployment rate (9.6%) as 2010 but produced only 2.1% NSW/GDP vs 8.6% in 2010. (4) Previous recessions did not produce such prolonged deviation between benefits and taxes.</t>
+          <t>The aim of this paper is to explain and interpret why neoliberal governments would tolerate a growing discrepancy between labor benefits and taxation. We are especially interested in accounting for the major post-2001 discrepancy in the net social wage data.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Moos_2017, Section 4 pp.6-7, Section 4.2.1 pp.17-19; full_transcription.md Sections 4 and 4.2.1</t>
+          <t>Moos 2017, Introduction, p.2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>validation_target</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>series_registry.json ES1305 validation reference_values: structural_shift = 0.030. This is the Moos-published magnitude of the post-2000 mean shift in NSW/EC. ST2 achieves structural_shift = 0.054 (DEC-013), which is larger due to NIPA vintage. Expected range for ES1305 is [-0.05, 0.10] for NSW/GDP values. The V11 validator should confirm: (1) pre-2000 mean approximately zero; (2) post-2000 mean substantially positive; (3) shift magnitude in plausible range.</t>
+          <t>ES1305 is ES1301 (NSW/GDP, 1959-2012) augmented with a post-2000 regime dummy or structural shift indicator. The purpose is to quantify and test the statistical significance of the break in the NSW/GDP series that appears after 2001. Moos identifies this as a major deviation from the Shaikh-Tonak pattern: the mean NSW/GDP for 2001-2012 is approximately 5% of GDP versus approximately 0% for 1959-2000.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md DEC-013; series_registry.json ES1305 validation</t>
+          <t>Moos_2017, Section 4 pp.6-7; full_transcription.md Section 4 The Net Social Wage in the 21st Century</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>causal_decomposition</t>
+          <t>decision_reference</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Moos Section 4 decomposes the post-2001 structural shift into four contributing factors: (1) Income support growth (dominant factor): E1 rising as share of GDP driven by Social Security expansion, Medicare/Medicaid growth (healthcare inflation 6.6%/yr 2000-2010), and refundable tax credits (EITC $1.3bn→$96.5bn from 1980-2010). (2) Tax cuts: Bush EGTRRA (2001) + JGTRRA (2003) reduced federal income tax revenue; extended under Obama through 2012. Tax revenue dropped sharply after dot-com bust (2001) and again after financial crisis (2008). (3) Unemployment intensity: 2010 intensity 31.46% vs 1983 18.95% at same 9.6% unemployment rate. (4) Demographic: Baby Boomer cohort aging, but peak eligibility (age 65+) not reached until 2011, so demographic shift explains gradual long-run trend but not sharp 2001 break.</t>
+          <t>[internal-decision-record] (2026-05-06): With E2 excluded from NSW computation (standard Shaikh-Tonak/Moos formula), ST2 P21 produces a structural shift of +0.054 across the 2000-2001 boundary (mean post-2000 minus mean pre-2000 for NSW/EC), compared to a structural shift of +0.030 in NSW/EC implied by Moos's published data. For NSW/GDP the analogous comparison: ST2 mean 1959-1997 = 0.013 vs Moos published 0.011. The structural shift is larger in ST2 than in Moos — attributable to NIPA vintage differences (2026 pull vs ~2015 pull).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Moos_2017, Section 4.1-4.2 pp.6-20; full_transcription.md Sections 4.1-4.2</t>
+          <t>[internal-decision-log] [internal-decision-record]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>robustness_check</t>
+          <t>structural_break_evidence</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Moos Section 4.3 confirms the structural shift is not an artifact of labor share measurement. Using Mohun (2016) alternative income share (declining from ~0.70 to ~0.45, much steeper than traditional LS 0.73→0.62) produces nearly identical NSW/GDP path. Maximum difference between traditional LS series and Mohun series is &lt;1 percentage point throughout 1959-2012. The post-2001 shift appears in both. This is because the shift is primarily driven by E1 (direct benefits, not multiplied by LS) and T2 cuts, not by changes in LS-weighted components.</t>
+          <t>Moos documents the post-2001 deviation as unprecedented in the history of the NSW series. Key evidence: (1) NSW/GDP was approximately 0.0065 in 2000, then rose to 8.6% in 2010. (2) The 1975 previous peak was much smaller (~2.9% of GDP in Moos series vs 8.6% in 2010). (3) The 1983 recession had the same official unemployment rate (9.6%) as 2010 but produced only 2.1% NSW/GDP vs 8.6% in 2010. (4) Previous recessions did not produce such prolonged deviation between benefits and taxes.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Moos_2017, Section 4.3 pp.20-23; full_transcription.md Section 4.3</t>
+          <t>Moos_2017, Section 4 pp.6-7, Section 4.2.1 pp.17-19; full_transcription.md Sections 4 and 4.2.1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>theoretical_interpretation</t>
+          <t>validation_target</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Moos's conclusion on the structural shift: a larger positive NSW does not indicate a more generous welfare state. Rather, it reflects (per de Brunhoff 1978 and Kotz 2015): state managing labor under neoliberal SSA by supplementing inadequate wages; state bearing costs of dysfunctional healthcare system it helped create; and automatic stabilizers responding to unprecedented long-term unemployment. A zero or modest NSW may indicate better worker conditions than a high positive NSW. The structural shift reveals the 'hidden cost' of neoliberalism to the fiscal state.</t>
+          <t>series_registry.json ES1305 validation reference_values: structural_shift = 0.030. This is the Moos-published magnitude of the post-2000 mean shift in NSW/EC. ST2 achieves structural_shift = 0.054 ([internal-decision-record]), which is larger due to NIPA vintage. Expected range for ES1305 is [-0.05, 0.10] for NSW/GDP values. The V11 validator should confirm: (1) pre-2000 mean approximately zero; (2) post-2000 mean substantially positive; (3) shift magnitude in plausible range.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Moos_2017, Section 5 pp.23-28, Section 6 pp.28-29; full_transcription.md Sections 5-6</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>[internal-decision-log] [internal-decision-record]; series_registry.json ES1305 validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>causal_decomposition</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Moos Section 4 decomposes the post-2001 structural shift into four contributing factors: (1) Income support growth (dominant factor): E1 rising as share of GDP driven by Social Security expansion, Medicare/Medicaid growth (healthcare inflation 6.6%/yr 2000-2010), and refundable tax credits (EITC $1.3bn→$96.5bn from 1980-2010). (2) Tax cuts: Bush EGTRRA (2001) + JGTRRA (2003) reduced federal income tax revenue; extended under Obama through 2012. Tax revenue dropped sharply after dot-com bust (2001) and again after financial crisis (2008). (3) Unemployment intensity: 2010 intensity 31.46% vs 1983 18.95% at same 9.6% unemployment rate. (4) Demographic: Baby Boomer cohort aging, but peak eligibility (age 65+) not reached until 2011, so demographic shift explains gradual long-run trend but not sharp 2001 break.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Moos_2017, Section 4.1-4.2 pp.6-20; full_transcription.md Sections 4.1-4.2</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>robustness_check</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ES1305 is ES1301 with post-2000 regime indicator added. Quantifies the structural break in NSW/GDP identified by Moos (2017) as the main contribution of her paper. Published structural shift = 0.030 (NSW/EC); ST2 achieves 0.054 (larger, NIPA vintage effect). Pre-2000 mean ~0%; post-2000 mean ~5% GDP. Caused by combination of income support growth, healthcare inflation, neoliberal tax cuts, and unprecedented unemployment intensity during Great Recession.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
+          <t>Moos Section 4.3 confirms the structural shift is not an artifact of labor share measurement. Using Mohun (2016) alternative income share (declining from ~0.70 to ~0.45, much steeper than traditional LS 0.73→0.62) produces nearly identical NSW/GDP path. Maximum difference between traditional LS series and Mohun series is &lt;1 percentage point throughout 1959-2012. The post-2001 shift appears in both. This is because the shift is primarily driven by E1 (direct benefits, not multiplied by LS) and T2 cuts, not by changes in LS-weighted components.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Moos_2017, Section 4.3 pp.20-23; full_transcription.md Section 4.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>theoretical_interpretation</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Moos's conclusion on the structural shift: a larger positive NSW does not indicate a more generous welfare state. Rather, it reflects (per de Brunhoff 1978 and Kotz 2015): state managing labor under neoliberal SSA by supplementing inadequate wages; state bearing costs of dysfunctional healthcare system it helped create; and automatic stabilizers responding to unprecedented long-term unemployment. A zero or modest NSW may indicate better worker conditions than a high positive NSW. The structural shift reveals the 'hidden cost' of neoliberalism to the fiscal state.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Moos_2017, Section 5 pp.23-28, Section 6 pp.28-29; full_transcription.md Sections 5-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ST2 structural shift of +0.054 exceeds Moos published +0.030; difference attributable to NIPA vintage (2026 vs ~2015 pull)</t>
-        </is>
-      </c>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ES1305 construction (add post-2000 regime dummy to ES1301) does not alter underlying NSW values; regime indicator is an analytical augmentation</t>
-        </is>
-      </c>
+          <t>Strikingly, the updated net social wage data reveals a sizable deviation starting in 2002, with much higher positive net social wages for a decade. In fact, the net social wage rises to a historic high of positive 8.6 percent of GDP in 2010.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
+          <t>the period 1959-2000 shows a mean NSW ≈ 0%, consistent with Shaikh and Tonak's findings. But the period 2001-2012 shows a mean NSW ≈ 5% of GDP, representing an unprecedented positive net transfer to workers.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>The aim of this paper is to explain and interpret why neoliberal governments would tolerate a growing discrepancy between labor benefits and taxation. We are especially interested in accounting for the major post-2001 discrepancy in the net social wage data.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ES1305 is ES1301 with post-2000 regime indicator added. Quantifies the structural break in NSW/GDP identified by Moos (2017) as the main contribution of her paper. Published structural shift = 0.030 (NSW/EC); ST2 achieves 0.054 (larger, NIPA vintage effect). Pre-2000 mean ~0%; post-2000 mean ~5% GDP. Caused by combination of income support growth, healthcare inflation, neoliberal tax cuts, and unprecedented unemployment intensity during Great Recession.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ST2 structural shift of +0.054 exceeds Moos published +0.030; difference attributable to NIPA vintage (2026 vs ~2015 pull)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ES1305 construction (add post-2000 regime dummy to ES1301) does not alter underlying NSW values; regime indicator is an analytical augmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>ACA (March 2010) falls within the study period; its effects on Medicare/Medicaid are partially captured but most enrollment expansions post-date 2012 endpoint</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>cross_references:</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
         <is>
           <t>ES1301</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
         <is>
           <t>ES1302</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
         <is>
           <t>ES1304</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Moos_2017</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Moos, Katherine A. 2017. 'Neoliberal Redistributive Policy: The U.S. Net Social Wage in the 21st Century.' Working Paper No. 2017-18, Department of Economics, University of Massachusetts Amherst. September 18, 2017.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>ST_2002</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 2002. 'The Rise and Fall of the U.S. Welfare State.' In Political Economy and Contemporary Capitalism. M.E. Sharpe, Armonk. pp. 247-265.</t>
         </is>
@@ -1412,11 +1533,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1479,7 +1600,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1621,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"structural_shift": 0.03}</t>
+          <t>{"1959": -0.025355084980274, "2012": 0.0564599479120065}</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1645,55 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>derived_statistics</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>{"structural_shift": 0.03}</t>
         </is>
       </c>
     </row>
